--- a/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:18</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
@@ -51,36 +51,36 @@
     <t xml:space="preserve">Pelluhue</t>
   </si>
   <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chanco</t>
   </si>
   <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sagrada Familia</t>
   </si>
   <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Río Claro</t>
   </si>
   <si>
-    <t xml:space="preserve">Rauco</t>
+    <t xml:space="preserve">Retiro</t>
   </si>
   <si>
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
-    <t xml:space="preserve">Retiro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
@@ -93,15 +93,15 @@
     <t xml:space="preserve">Linares</t>
   </si>
   <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
     <t xml:space="preserve">Molina</t>
   </si>
   <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
     <t xml:space="preserve">Romeral</t>
   </si>
   <si>
@@ -111,12 +111,12 @@
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
+    <t xml:space="preserve">Colbún</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Javier</t>
   </si>
   <si>
-    <t xml:space="preserve">Colbún</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curicó</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -565,7 +565,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>199.45</v>
+        <v>216.12</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>162.96</v>
+        <v>174.86</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>158.59</v>
+        <v>171.4</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>157.18</v>
+        <v>170.35</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>143.53</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="7">
@@ -644,13 +644,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7202</v>
+        <v>7303</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>141.16</v>
+        <v>153.03</v>
       </c>
     </row>
     <row r="8">
@@ -661,13 +661,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7303</v>
+        <v>7202</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>140.49</v>
+        <v>150.95</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +684,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>130.55</v>
+        <v>140.23</v>
       </c>
     </row>
     <row r="10">
@@ -695,13 +695,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7407</v>
+        <v>7106</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>125.26</v>
+        <v>134.22</v>
       </c>
     </row>
     <row r="11">
@@ -712,13 +712,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7106</v>
+        <v>7407</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>124.65</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>122.41</v>
+        <v>132.38</v>
       </c>
     </row>
     <row r="13">
@@ -746,13 +746,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7108</v>
+        <v>7305</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>120.54</v>
+        <v>129.33</v>
       </c>
     </row>
     <row r="14">
@@ -763,13 +763,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7305</v>
+        <v>7108</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>120.37</v>
+        <v>128.48</v>
       </c>
     </row>
     <row r="15">
@@ -780,13 +780,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7404</v>
+        <v>7405</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>118.45</v>
+        <v>127.02</v>
       </c>
     </row>
     <row r="16">
@@ -797,13 +797,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7405</v>
+        <v>7404</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>118.29</v>
+        <v>126.57</v>
       </c>
     </row>
     <row r="17">
@@ -820,7 +820,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>116.31</v>
+        <v>125.89</v>
       </c>
     </row>
     <row r="18">
@@ -837,7 +837,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>114.23</v>
+        <v>122.6</v>
       </c>
     </row>
     <row r="19">
@@ -854,7 +854,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>113.86</v>
+        <v>122.12</v>
       </c>
     </row>
     <row r="20">
@@ -871,7 +871,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>111.67</v>
+        <v>120.06</v>
       </c>
     </row>
     <row r="21">
@@ -882,13 +882,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7101</v>
+        <v>7104</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>107.05</v>
+        <v>115.94</v>
       </c>
     </row>
     <row r="22">
@@ -899,13 +899,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>7304</v>
+        <v>7101</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>105.91</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="23">
@@ -916,13 +916,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7104</v>
+        <v>7304</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>105.9</v>
+        <v>113.96</v>
       </c>
     </row>
     <row r="24">
@@ -939,7 +939,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>105.71</v>
+        <v>113.39</v>
       </c>
     </row>
     <row r="25">
@@ -956,7 +956,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>105.27</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="26">
@@ -973,7 +973,7 @@
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>105.11</v>
+        <v>112.93</v>
       </c>
     </row>
     <row r="27">
@@ -984,13 +984,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7406</v>
+        <v>7402</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>104.28</v>
+        <v>111.83</v>
       </c>
     </row>
     <row r="28">
@@ -1001,13 +1001,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7402</v>
+        <v>7406</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>104.19</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="29">
@@ -1024,7 +1024,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>95.94</v>
+        <v>102.71</v>
       </c>
     </row>
     <row r="30">
@@ -1041,7 +1041,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>93.72</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="31">
@@ -1058,7 +1058,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>53.39</v>
+        <v>57.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:03</t>
+    <t xml:space="preserve">2026-10-05 16:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
